--- a/Experiment_5/results/Experiment_5_results.xlsx
+++ b/Experiment_5/results/Experiment_5_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="95">
   <si>
     <t>phoenixTrain VITEKTest</t>
   </si>
@@ -302,10 +302,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -343,6 +344,12 @@
     <font>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -427,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -459,16 +466,16 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -484,7 +491,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -498,13 +505,17 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -513,25 +524,22 @@
     <xf borderId="1" fillId="9" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -773,11 +781,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="950518415"/>
-        <c:axId val="625847163"/>
+        <c:axId val="170180077"/>
+        <c:axId val="1312356759"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="950518415"/>
+        <c:axId val="170180077"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -833,10 +841,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625847163"/>
+        <c:crossAx val="1312356759"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="625847163"/>
+        <c:axId val="1312356759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.7"/>
@@ -914,7 +922,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="950518415"/>
+        <c:crossAx val="170180077"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -923,286 +931,6 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0" sz="3000">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="3000">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Median ROC</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.05"/>
-          <c:y val="0.02132936507936508"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Median ROC Phoenix Train</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFC106"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1600"/>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>EKP_NA_Conclusio_CV!$N$205:$P$205</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>EKP_NA_Conclusio_CV!$N$206:$P$206</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Median ROC Mixed Train</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="D81A60"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1600"/>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>EKP_NA_Conclusio_CV!$N$205:$P$205</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>EKP_NA_Conclusio_CV!$N$207:$P$207</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="2100070818"/>
-        <c:axId val="952154127"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2100070818"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:spPr>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0" sz="1800">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="952154127"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="952154127"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0.7"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2100070818"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -1338,11 +1066,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="132099087"/>
-        <c:axId val="1894024261"/>
+        <c:axId val="2128105276"/>
+        <c:axId val="210368223"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="132099087"/>
+        <c:axId val="2128105276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1398,10 +1126,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1894024261"/>
+        <c:crossAx val="210368223"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1894024261"/>
+        <c:axId val="210368223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.96"/>
@@ -1479,7 +1207,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="132099087"/>
+        <c:crossAx val="2128105276"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1487,7 +1215,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -1633,11 +1361,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="885783876"/>
-        <c:axId val="2005105419"/>
+        <c:axId val="880269186"/>
+        <c:axId val="986632222"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="885783876"/>
+        <c:axId val="880269186"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1693,10 +1421,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2005105419"/>
+        <c:crossAx val="986632222"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2005105419"/>
+        <c:axId val="986632222"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.7"/>
@@ -1774,7 +1502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="885783876"/>
+        <c:crossAx val="880269186"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1808,7 +1536,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:plotArea>
@@ -1910,11 +1638,39 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1328279899"/>
-        <c:axId val="914194025"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EKP_NA_Conclusio_CV!$C$307</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>EKP_NA_Conclusio_CV!$D$304:$F$304</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EKP_NA_Conclusio_CV!$D$307:$F$307</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1298048268"/>
+        <c:axId val="1436911400"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1328279899"/>
+        <c:axId val="1298048268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1970,10 +1726,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="914194025"/>
+        <c:crossAx val="1436911400"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="914194025"/>
+        <c:axId val="1436911400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.981"/>
@@ -2051,7 +1807,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1328279899"/>
+        <c:crossAx val="1298048268"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2077,7 +1833,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -2210,11 +1966,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1738115587"/>
-        <c:axId val="2079144455"/>
+        <c:axId val="825487506"/>
+        <c:axId val="1620317667"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1738115587"/>
+        <c:axId val="825487506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2270,10 +2026,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2079144455"/>
+        <c:crossAx val="1620317667"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2079144455"/>
+        <c:axId val="1620317667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0"/>
@@ -2351,7 +2107,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1738115587"/>
+        <c:crossAx val="825487506"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2359,7 +2115,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -2498,11 +2254,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1376863356"/>
-        <c:axId val="1698848856"/>
+        <c:axId val="2064197238"/>
+        <c:axId val="1024458502"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1376863356"/>
+        <c:axId val="2064197238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2558,10 +2314,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1698848856"/>
+        <c:crossAx val="1024458502"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1698848856"/>
+        <c:axId val="1024458502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0"/>
@@ -2639,7 +2395,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1376863356"/>
+        <c:crossAx val="2064197238"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2673,7 +2429,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
   <c:chart>
     <c:title>
@@ -2803,11 +2559,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="431676803"/>
-        <c:axId val="676552440"/>
+        <c:axId val="1543923571"/>
+        <c:axId val="1172246684"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="431676803"/>
+        <c:axId val="1543923571"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2863,10 +2619,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676552440"/>
+        <c:crossAx val="1172246684"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="676552440"/>
+        <c:axId val="1172246684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.0"/>
@@ -2944,7 +2700,287 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431676803"/>
+        <c:crossAx val="1543923571"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0" sz="3000">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="3000">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Median ROC</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.05"/>
+          <c:y val="0.02132936507936508"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Median ROC Phoenix Train</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC106"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr sz="1600"/>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>EKP_NA_Conclusio_CV!$N$205:$P$205</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EKP_NA_Conclusio_CV!$N$206:$P$206</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Median ROC Mixed Train</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D81A60"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr sz="1600"/>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>EKP_NA_Conclusio_CV!$N$205:$P$205</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EKP_NA_Conclusio_CV!$N$207:$P$207</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="892729437"/>
+        <c:axId val="1696379830"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="892729437"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0" sz="1800">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1696379830"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1696379830"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.7"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892729437"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2956,10 +2992,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3952875" cy="4800600"/>
     <xdr:graphicFrame>
@@ -2981,10 +3017,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3952875" cy="4800600"/>
     <xdr:graphicFrame>
@@ -3006,12 +3042,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>194</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3952875" cy="4800600"/>
+    <xdr:ext cx="5448300" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 3" title="Chart"/>
@@ -3031,12 +3067,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>217</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5448300" cy="3533775"/>
+    <xdr:ext cx="4152900" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 4" title="Chart"/>
@@ -3056,12 +3092,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>306</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>285</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4152900" cy="3533775"/>
+    <xdr:ext cx="3638550" cy="4352925"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="5" name="Chart 5" title="Chart"/>
@@ -3082,11 +3118,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>285</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>313</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3638550" cy="4352925"/>
+    <xdr:ext cx="3581400" cy="4419600"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="6" name="Chart 6" title="Chart"/>
@@ -3106,8 +3142,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>313</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
@@ -3131,12 +3167,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>313</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3581400" cy="4419600"/>
+    <xdr:ext cx="3952875" cy="4800600"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="8" name="Chart 8" title="Chart"/>
@@ -15205,7 +15241,7 @@
         <v>12.85734536</v>
       </c>
       <c r="R175" s="19">
-        <f t="shared" ref="R175:X175" si="31">MEDIAN(R172:R174)</f>
+        <f t="shared" ref="R175:Y175" si="31">MEDIAN(R172:R174)</f>
         <v>0.02050364383</v>
       </c>
       <c r="S175" s="19">
@@ -15231,6 +15267,10 @@
       <c r="X175" s="19">
         <f t="shared" si="31"/>
         <v>2.383098534</v>
+      </c>
+      <c r="Y175" s="19">
+        <f t="shared" si="31"/>
+        <v>1.398268931</v>
       </c>
       <c r="AB175" s="14" t="s">
         <v>16</v>
@@ -17519,6 +17559,21 @@
       <c r="P216" s="20" t="s">
         <v>7</v>
       </c>
+      <c r="R216" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="S216" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="T216" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="U216" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="V216" s="20" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="217">
       <c r="C217" s="14" t="s">
@@ -17571,6 +17626,24 @@
         <f t="shared" ref="P217:P218" si="64">I220</f>
         <v>0.7853648848</v>
       </c>
+      <c r="R217" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="S217" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="T217" s="19">
+        <f>K168</f>
+        <v>6.266666667</v>
+      </c>
+      <c r="U217" s="19">
+        <f>K161</f>
+        <v>5.533333333</v>
+      </c>
+      <c r="V217" s="19">
+        <f>K175</f>
+        <v>12.85734536</v>
+      </c>
     </row>
     <row r="218">
       <c r="M218" s="14" t="s">
@@ -17588,6 +17661,24 @@
         <f t="shared" si="64"/>
         <v>0.8779605633</v>
       </c>
+      <c r="R218" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="S218" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T218" s="19">
+        <f>K189</f>
+        <v>4.943575063</v>
+      </c>
+      <c r="U218" s="19">
+        <f>K182</f>
+        <v>4.066666667</v>
+      </c>
+      <c r="V218" s="19">
+        <f>K196</f>
+        <v>6.907718147</v>
+      </c>
     </row>
     <row r="219">
       <c r="C219" s="26" t="s">
@@ -17617,6 +17708,24 @@
       <c r="K219" s="20" t="s">
         <v>9</v>
       </c>
+      <c r="R219" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S219" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="T219" s="19">
+        <f>J168</f>
+        <v>6.466666667</v>
+      </c>
+      <c r="U219" s="19">
+        <f>J161</f>
+        <v>11.55510669</v>
+      </c>
+      <c r="V219" s="19">
+        <f>J175</f>
+        <v>13.12634923</v>
+      </c>
     </row>
     <row r="220">
       <c r="C220" s="14" t="s">
@@ -17654,6 +17763,24 @@
         <f t="shared" si="65"/>
         <v>7.2</v>
       </c>
+      <c r="R220" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S220" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T220" s="19">
+        <f>J189</f>
+        <v>3.146189649</v>
+      </c>
+      <c r="U220" s="19">
+        <f>J182</f>
+        <v>6.252106292</v>
+      </c>
+      <c r="V220" s="19">
+        <f>J196</f>
+        <v>11.52122184</v>
+      </c>
     </row>
     <row r="221">
       <c r="C221" s="14" t="s">
@@ -17693,19 +17820,26 @@
       </c>
     </row>
     <row r="222">
-      <c r="M222" s="27"/>
-      <c r="N222" s="28" t="s">
+      <c r="D222" s="28">
+        <f>D221-D220</f>
+        <v>0.0670807779</v>
+      </c>
+      <c r="M222" s="29"/>
+      <c r="N222" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="O222" s="28" t="s">
+      <c r="O222" s="30" t="s">
         <v>62</v>
+      </c>
+      <c r="R222" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="223">
       <c r="C223" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M223" s="27" t="s">
+      <c r="M223" s="29" t="s">
         <v>74</v>
       </c>
       <c r="N223" s="17">
@@ -17713,6 +17847,21 @@
       </c>
       <c r="O223" s="17">
         <v>980.0</v>
+      </c>
+      <c r="R223" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="S223" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="T223" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="U223" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="V223" s="20" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="224">
@@ -17728,7 +17877,7 @@
       <c r="F224" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="M224" s="27" t="s">
+      <c r="M224" s="29" t="s">
         <v>75</v>
       </c>
       <c r="N224" s="17">
@@ -17736,6 +17885,24 @@
       </c>
       <c r="O224" s="17">
         <v>1030.0</v>
+      </c>
+      <c r="R224" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="S224" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="T224" s="19">
+        <f>Y168</f>
+        <v>1.203698006</v>
+      </c>
+      <c r="U224" s="19">
+        <f>Y161</f>
+        <v>1.388844444</v>
+      </c>
+      <c r="V224" s="19">
+        <f>Y175</f>
+        <v>1.398268931</v>
       </c>
     </row>
     <row r="225">
@@ -17754,7 +17921,7 @@
         <f>MEDIAN(W158:W160,W165:W167,W172:W174)</f>
         <v>0.01959702597</v>
       </c>
-      <c r="M225" s="27" t="s">
+      <c r="M225" s="29" t="s">
         <v>76</v>
       </c>
       <c r="N225" s="17">
@@ -17762,6 +17929,24 @@
       </c>
       <c r="O225" s="17">
         <v>904.0</v>
+      </c>
+      <c r="R225" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="S225" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T225" s="19">
+        <f>Y189</f>
+        <v>0.8793937306</v>
+      </c>
+      <c r="U225" s="19">
+        <f>Y182</f>
+        <v>1.066666667</v>
+      </c>
+      <c r="V225" s="19">
+        <f>Y196</f>
+        <v>2.156801329</v>
       </c>
     </row>
     <row r="226">
@@ -17790,6 +17975,44 @@
       <c r="O226" s="24">
         <f t="shared" si="69"/>
         <v>980</v>
+      </c>
+      <c r="R226" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S226" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="T226" s="19">
+        <f>X168</f>
+        <v>1.5860503</v>
+      </c>
+      <c r="U226" s="19">
+        <f>X161</f>
+        <v>1.925270544</v>
+      </c>
+      <c r="V226" s="19">
+        <f>X175</f>
+        <v>2.383098534</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="R227" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S227" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T227" s="19">
+        <f>X189</f>
+        <v>1.892675942</v>
+      </c>
+      <c r="U227" s="19">
+        <f>X182</f>
+        <v>1.326649916</v>
+      </c>
+      <c r="V227" s="19">
+        <f>X196</f>
+        <v>2.798438876</v>
       </c>
     </row>
     <row r="230">
@@ -18632,59 +18855,59 @@
         <f t="shared" si="72"/>
         <v>4.838227595</v>
       </c>
-      <c r="L242" s="29">
+      <c r="L242" s="31">
         <f t="shared" si="72"/>
         <v>74</v>
       </c>
-      <c r="M242" s="29">
+      <c r="M242" s="31">
         <f t="shared" si="72"/>
         <v>157.4</v>
       </c>
-      <c r="N242" s="29">
+      <c r="N242" s="31">
         <f t="shared" si="72"/>
         <v>242.7</v>
       </c>
-      <c r="O242" s="29">
+      <c r="O242" s="31">
         <f t="shared" si="72"/>
         <v>387.9</v>
       </c>
-      <c r="P242" s="29">
+      <c r="P242" s="31">
         <f t="shared" si="72"/>
         <v>780.3</v>
       </c>
-      <c r="Q242" s="29">
+      <c r="Q242" s="31">
         <f t="shared" si="72"/>
         <v>1200</v>
       </c>
-      <c r="R242" s="29">
+      <c r="R242" s="31">
         <f t="shared" si="72"/>
         <v>0.01831007431</v>
       </c>
-      <c r="S242" s="29">
+      <c r="S242" s="31">
         <f t="shared" si="72"/>
         <v>0.03160243628</v>
       </c>
-      <c r="T242" s="29">
+      <c r="T242" s="31">
         <f t="shared" si="72"/>
         <v>0.02429269712</v>
       </c>
-      <c r="U242" s="29">
+      <c r="U242" s="31">
         <f t="shared" si="72"/>
         <v>0.01570996341</v>
       </c>
-      <c r="V242" s="29">
+      <c r="V242" s="31">
         <f t="shared" si="72"/>
         <v>0.02114387238</v>
       </c>
-      <c r="W242" s="29">
+      <c r="W242" s="31">
         <f t="shared" si="72"/>
         <v>0.02266196599</v>
       </c>
-      <c r="X242" s="29">
+      <c r="X242" s="31">
         <f t="shared" si="72"/>
         <v>1.577271569</v>
       </c>
-      <c r="Y242" s="29">
+      <c r="Y242" s="31">
         <f t="shared" si="72"/>
         <v>0.6747818081</v>
       </c>
@@ -19029,7 +19252,7 @@
         <f t="shared" si="73"/>
         <v>300</v>
       </c>
-      <c r="O248" s="30">
+      <c r="O248" s="32">
         <v>109.2</v>
       </c>
       <c r="P248" s="17">
@@ -19591,10 +19814,10 @@
     <row r="255">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
-      <c r="AA255" s="31"/>
-      <c r="AB255" s="29"/>
-      <c r="AC255" s="29"/>
-      <c r="AD255" s="29"/>
+      <c r="AA255" s="33"/>
+      <c r="AB255" s="31"/>
+      <c r="AC255" s="31"/>
+      <c r="AD255" s="31"/>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
@@ -19703,7 +19926,7 @@
         <v>9</v>
       </c>
       <c r="Z257" s="1"/>
-      <c r="AA257" s="32"/>
+      <c r="AA257" s="34"/>
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
@@ -19908,7 +20131,7 @@
         <f t="shared" si="76"/>
         <v>177.2</v>
       </c>
-      <c r="O260" s="30">
+      <c r="O260" s="32">
         <v>109.2</v>
       </c>
       <c r="P260" s="17">
@@ -20117,7 +20340,7 @@
     <row r="263">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
-      <c r="C263" s="33" t="s">
+      <c r="C263" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D263" s="18">
@@ -20199,7 +20422,7 @@
     <row r="264">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
-      <c r="C264" s="33" t="s">
+      <c r="C264" s="35" t="s">
         <v>28</v>
       </c>
       <c r="D264" s="15">
@@ -20281,7 +20504,7 @@
     <row r="265">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
-      <c r="C265" s="33" t="s">
+      <c r="C265" s="35" t="s">
         <v>29</v>
       </c>
       <c r="D265" s="18">
@@ -20398,59 +20621,59 @@
         <f t="shared" si="78"/>
         <v>4.759098916</v>
       </c>
-      <c r="L266" s="29">
+      <c r="L266" s="31">
         <f t="shared" si="78"/>
         <v>43.8</v>
       </c>
-      <c r="M266" s="29">
+      <c r="M266" s="31">
         <f t="shared" si="78"/>
         <v>65.4</v>
       </c>
-      <c r="N266" s="29">
+      <c r="N266" s="31">
         <f t="shared" si="78"/>
         <v>134.8</v>
       </c>
-      <c r="O266" s="29">
+      <c r="O266" s="31">
         <f t="shared" si="78"/>
         <v>387.9</v>
       </c>
-      <c r="P266" s="29">
+      <c r="P266" s="31">
         <f t="shared" si="78"/>
         <v>780.3</v>
       </c>
-      <c r="Q266" s="29">
+      <c r="Q266" s="31">
         <f t="shared" si="78"/>
         <v>1200</v>
       </c>
-      <c r="R266" s="29">
+      <c r="R266" s="31">
         <f t="shared" si="78"/>
         <v>0.02290358189</v>
       </c>
-      <c r="S266" s="29">
+      <c r="S266" s="31">
         <f t="shared" si="78"/>
         <v>0.01903685315</v>
       </c>
-      <c r="T266" s="29">
+      <c r="T266" s="31">
         <f t="shared" si="78"/>
         <v>0.02205952434</v>
       </c>
-      <c r="U266" s="29">
+      <c r="U266" s="31">
         <f t="shared" si="78"/>
         <v>0.01973983699</v>
       </c>
-      <c r="V266" s="29">
+      <c r="V266" s="31">
         <f t="shared" si="78"/>
         <v>0.03162491617</v>
       </c>
-      <c r="W266" s="29">
+      <c r="W266" s="31">
         <f t="shared" si="78"/>
         <v>0.02299978931</v>
       </c>
-      <c r="X266" s="29">
+      <c r="X266" s="31">
         <f t="shared" si="78"/>
         <v>2.431918192</v>
       </c>
-      <c r="Y266" s="29">
+      <c r="Y266" s="31">
         <f t="shared" si="78"/>
         <v>1.685944985</v>
       </c>
@@ -20719,7 +20942,7 @@
       <c r="P271" s="17">
         <v>695.8</v>
       </c>
-      <c r="Q271" s="30">
+      <c r="Q271" s="32">
         <f t="shared" si="80"/>
         <v>896.4</v>
       </c>
@@ -20793,7 +21016,7 @@
         <f t="shared" si="79"/>
         <v>300</v>
       </c>
-      <c r="O272" s="30">
+      <c r="O272" s="32">
         <v>106.2</v>
       </c>
       <c r="P272" s="17">
@@ -20967,7 +21190,7 @@
       <c r="P274" s="17">
         <v>397.2</v>
       </c>
-      <c r="Q274" s="30">
+      <c r="Q274" s="32">
         <f t="shared" si="80"/>
         <v>874.6</v>
       </c>
@@ -20999,7 +21222,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="21"/>
       <c r="AC274" s="21"/>
-      <c r="AD274" s="34"/>
+      <c r="AD274" s="36"/>
       <c r="AE274" s="14" t="s">
         <v>20</v>
       </c>
@@ -21008,7 +21231,7 @@
     <row r="275">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
-      <c r="C275" s="33" t="s">
+      <c r="C275" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D275" s="18">
@@ -21051,7 +21274,7 @@
       <c r="P275" s="17">
         <v>573.8</v>
       </c>
-      <c r="Q275" s="30">
+      <c r="Q275" s="32">
         <f t="shared" si="80"/>
         <v>797.2</v>
       </c>
@@ -21167,7 +21390,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="21"/>
       <c r="AC276" s="21"/>
-      <c r="AD276" s="34"/>
+      <c r="AD276" s="36"/>
       <c r="AE276" s="14" t="s">
         <v>24</v>
       </c>
@@ -21219,7 +21442,7 @@
       <c r="P277" s="17">
         <v>550.8</v>
       </c>
-      <c r="Q277" s="30">
+      <c r="Q277" s="32">
         <f t="shared" si="80"/>
         <v>854</v>
       </c>
@@ -21251,7 +21474,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="21"/>
       <c r="AC277" s="21"/>
-      <c r="AD277" s="34"/>
+      <c r="AD277" s="36"/>
       <c r="AE277" s="14" t="s">
         <v>26</v>
       </c>
@@ -21612,7 +21835,7 @@
       <c r="P283" s="17">
         <v>695.8</v>
       </c>
-      <c r="Q283" s="30">
+      <c r="Q283" s="32">
         <f t="shared" si="83"/>
         <v>896.4</v>
       </c>
@@ -21690,7 +21913,7 @@
         <f t="shared" si="82"/>
         <v>300</v>
       </c>
-      <c r="O284" s="30">
+      <c r="O284" s="32">
         <v>106.2</v>
       </c>
       <c r="P284" s="17">
@@ -21864,7 +22087,7 @@
       <c r="P286" s="17">
         <v>397.2</v>
       </c>
-      <c r="Q286" s="30">
+      <c r="Q286" s="32">
         <f t="shared" si="83"/>
         <v>874.6</v>
       </c>
@@ -21905,7 +22128,7 @@
     <row r="287">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
-      <c r="C287" s="33" t="s">
+      <c r="C287" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D287" s="15">
@@ -21948,7 +22171,7 @@
       <c r="P287" s="17">
         <v>573.8</v>
       </c>
-      <c r="Q287" s="30">
+      <c r="Q287" s="32">
         <f t="shared" si="83"/>
         <v>797.2</v>
       </c>
@@ -22116,7 +22339,7 @@
       <c r="P289" s="17">
         <v>550.8</v>
       </c>
-      <c r="Q289" s="30">
+      <c r="Q289" s="32">
         <f t="shared" si="83"/>
         <v>854</v>
       </c>
@@ -22487,7 +22710,7 @@
       <c r="P295" s="17">
         <v>695.8</v>
       </c>
-      <c r="Q295" s="30">
+      <c r="Q295" s="32">
         <f t="shared" si="86"/>
         <v>896.4</v>
       </c>
@@ -22563,7 +22786,7 @@
         <f t="shared" si="85"/>
         <v>177.2</v>
       </c>
-      <c r="O296" s="30">
+      <c r="O296" s="32">
         <v>106.2</v>
       </c>
       <c r="P296" s="17">
@@ -22733,7 +22956,7 @@
       <c r="P298" s="17">
         <v>397.2</v>
       </c>
-      <c r="Q298" s="30">
+      <c r="Q298" s="32">
         <f t="shared" si="86"/>
         <v>874.6</v>
       </c>
@@ -22772,7 +22995,7 @@
     <row r="299">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
-      <c r="C299" s="33" t="s">
+      <c r="C299" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D299" s="15">
@@ -22815,7 +23038,7 @@
       <c r="P299" s="17">
         <v>573.8</v>
       </c>
-      <c r="Q299" s="30">
+      <c r="Q299" s="32">
         <f t="shared" si="86"/>
         <v>797.2</v>
       </c>
@@ -22979,7 +23202,7 @@
       <c r="P301" s="17">
         <v>550.8</v>
       </c>
-      <c r="Q301" s="30">
+      <c r="Q301" s="32">
         <f t="shared" si="86"/>
         <v>854</v>
       </c>
@@ -23121,11 +23344,11 @@
       <c r="F304" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H304" s="27"/>
-      <c r="I304" s="28" t="s">
+      <c r="H304" s="29"/>
+      <c r="I304" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="J304" s="28" t="s">
+      <c r="J304" s="30" t="s">
         <v>62</v>
       </c>
       <c r="L304" s="20" t="s">
@@ -23172,7 +23395,7 @@
         <f>MEDIAN(I234:I241,I246:I253,I258:I265)</f>
         <v>0.7978651025</v>
       </c>
-      <c r="H305" s="35" t="s">
+      <c r="H305" s="27" t="s">
         <v>74</v>
       </c>
       <c r="I305" s="17">
@@ -23231,7 +23454,7 @@
         <f>MEDIAN(I270:I277,I282:I289,I294:I301)</f>
         <v>0.7225657347</v>
       </c>
-      <c r="H306" s="35" t="s">
+      <c r="H306" s="27" t="s">
         <v>78</v>
       </c>
       <c r="I306" s="17">
@@ -23275,7 +23498,11 @@
       </c>
     </row>
     <row r="307">
-      <c r="H307" s="35" t="s">
+      <c r="D307" s="19">
+        <f>D306-D305</f>
+        <v>0.02917526018</v>
+      </c>
+      <c r="H307" s="27" t="s">
         <v>79</v>
       </c>
       <c r="I307" s="17">
@@ -23307,7 +23534,7 @@
       <c r="C308" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H308" s="35" t="s">
+      <c r="H308" s="27" t="s">
         <v>75</v>
       </c>
       <c r="I308" s="17">
@@ -23360,7 +23587,7 @@
       <c r="F309" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H309" s="35" t="s">
+      <c r="H309" s="27" t="s">
         <v>80</v>
       </c>
       <c r="I309" s="17">
@@ -23419,7 +23646,7 @@
         <f>MEDIAN(W234:W241,W246:W253,W258:W265)</f>
         <v>0.01888268772</v>
       </c>
-      <c r="H310" s="35" t="s">
+      <c r="H310" s="27" t="s">
         <v>81</v>
       </c>
       <c r="I310" s="17">
@@ -23478,7 +23705,7 @@
         <f>MEDIAN(W294:W301,W282:W289,W270:W277)</f>
         <v>0.02034190004</v>
       </c>
-      <c r="H311" s="35" t="s">
+      <c r="H311" s="27" t="s">
         <v>82</v>
       </c>
       <c r="I311" s="17">
@@ -23489,7 +23716,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="H312" s="35" t="s">
+      <c r="H312" s="27" t="s">
         <v>76</v>
       </c>
       <c r="I312" s="17">
@@ -23696,31 +23923,166 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="36"/>
-      <c r="B321" s="37"/>
-      <c r="C321" s="37" t="s">
+      <c r="A321" s="37"/>
+      <c r="B321" s="38"/>
+      <c r="C321" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D321" s="37" t="s">
+      <c r="D321" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="E321" s="37" t="s">
+      <c r="E321" s="38" t="s">
         <v>86</v>
       </c>
+      <c r="Q321" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="R321" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="S321" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="T321" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="U321" s="20" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="322">
-      <c r="A322" s="36"/>
-      <c r="B322" s="37" t="s">
+      <c r="A322" s="37"/>
+      <c r="B322" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="C322" s="38">
+      <c r="C322" s="39">
         <v>0.027344</v>
       </c>
       <c r="D322" s="15">
         <v>0.0625</v>
       </c>
-      <c r="E322" s="38">
+      <c r="E322" s="39">
         <v>0.039062</v>
+      </c>
+      <c r="Q322" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="R322" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="S322" s="19">
+        <f>K254</f>
+        <v>3.966666667</v>
+      </c>
+      <c r="T322" s="19">
+        <f>K242</f>
+        <v>4.838227595</v>
+      </c>
+      <c r="U322" s="19">
+        <f>K278</f>
+        <v>7.033035497</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="Q323" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="R323" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="S323" s="19">
+        <f>K290</f>
+        <v>8.566666667</v>
+      </c>
+      <c r="T323" s="19">
+        <f>K278</f>
+        <v>7.033035497</v>
+      </c>
+      <c r="U323" s="19">
+        <f>K302</f>
+        <v>14.75501933</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="Q324" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R324" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="S324" s="19">
+        <f>J254</f>
+        <v>5.966666667</v>
+      </c>
+      <c r="T324" s="19">
+        <f>J242</f>
+        <v>19.83333333</v>
+      </c>
+      <c r="U324" s="19">
+        <f>J266</f>
+        <v>9.724408779</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="Q325" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R325" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="S325" s="19">
+        <f>J290</f>
+        <v>5</v>
+      </c>
+      <c r="T325" s="19">
+        <f>J278</f>
+        <v>2.673257696</v>
+      </c>
+      <c r="U325" s="19">
+        <f>J302</f>
+        <v>3.668911276</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="Q327" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="Q328" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="R328" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="S328" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="T328" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="U328" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="Q329" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="R329" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="S329" s="19">
+        <f>Y254</f>
+        <v>0.9094134381</v>
+      </c>
+      <c r="T329" s="19">
+        <f>Y242</f>
+        <v>0.6747818081</v>
+      </c>
+      <c r="U329" s="19">
+        <f>Y266</f>
+        <v>1.685944985</v>
       </c>
     </row>
     <row r="330">
@@ -23748,6 +24110,24 @@
       <c r="I330" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="Q330" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="R330" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="S330" s="19">
+        <f>Y290</f>
+        <v>1.24555963</v>
+      </c>
+      <c r="T330" s="19">
+        <f>Y278</f>
+        <v>1.215160883</v>
+      </c>
+      <c r="U330" s="19">
+        <f>Y302</f>
+        <v>2.27280784</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
@@ -23756,96 +24136,132 @@
       <c r="F331" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="Q331" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R331" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="S331" s="19">
+        <f>X254</f>
+        <v>1.269120379</v>
+      </c>
+      <c r="T331" s="19">
+        <f>X242</f>
+        <v>1.577271569</v>
+      </c>
+      <c r="U331" s="19">
+        <f>X266</f>
+        <v>2.431918192</v>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="35" t="s">
+      <c r="A332" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B332" s="39">
+      <c r="B332" s="40">
         <v>618.0</v>
       </c>
-      <c r="C332" s="39">
+      <c r="C332" s="40">
         <v>230.0</v>
       </c>
-      <c r="D332" s="39">
+      <c r="D332" s="40">
         <v>848.0</v>
       </c>
       <c r="F332" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G332" s="40">
+      <c r="G332" s="41">
         <v>618.0</v>
       </c>
-      <c r="H332" s="40">
+      <c r="H332" s="41">
         <v>230.0</v>
       </c>
-      <c r="I332" s="40">
+      <c r="I332" s="41">
         <v>848.0</v>
       </c>
+      <c r="Q332" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R332" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="S332" s="19">
+        <f>X290</f>
+        <v>1.544299739</v>
+      </c>
+      <c r="T332" s="19">
+        <f>Y278</f>
+        <v>1.215160883</v>
+      </c>
+      <c r="U332" s="19">
+        <f>X302</f>
+        <v>1.650477446</v>
+      </c>
     </row>
     <row r="333">
-      <c r="A333" s="35" t="s">
+      <c r="A333" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B333" s="39">
+      <c r="B333" s="40">
         <v>99.0</v>
       </c>
-      <c r="C333" s="39">
+      <c r="C333" s="40">
         <v>593.0</v>
       </c>
-      <c r="D333" s="39">
+      <c r="D333" s="40">
         <v>692.0</v>
       </c>
       <c r="F333" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G333" s="40">
+      <c r="G333" s="41">
         <v>426.0</v>
       </c>
-      <c r="H333" s="40">
+      <c r="H333" s="41">
         <v>422.0</v>
       </c>
-      <c r="I333" s="40">
+      <c r="I333" s="41">
         <v>848.0</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="35" t="s">
+      <c r="A334" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B334" s="39">
+      <c r="B334" s="40">
         <v>84.0</v>
       </c>
-      <c r="C334" s="39">
+      <c r="C334" s="40">
         <v>764.0</v>
       </c>
-      <c r="D334" s="39">
+      <c r="D334" s="40">
         <v>848.0</v>
       </c>
       <c r="F334" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G334" s="40">
+      <c r="G334" s="41">
         <v>226.0</v>
       </c>
-      <c r="H334" s="40">
+      <c r="H334" s="41">
         <v>467.0</v>
       </c>
-      <c r="I334" s="40">
+      <c r="I334" s="41">
         <v>693.0</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="35" t="s">
+      <c r="A335" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B335" s="39">
+      <c r="B335" s="40">
         <v>426.0</v>
       </c>
-      <c r="C335" s="39">
+      <c r="C335" s="40">
         <v>422.0</v>
       </c>
-      <c r="D335" s="39">
+      <c r="D335" s="40">
         <v>848.0</v>
       </c>
       <c r="F335" s="2" t="s">
@@ -23853,94 +24269,94 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="35" t="s">
+      <c r="A336" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B336" s="39">
+      <c r="B336" s="40">
         <v>102.0</v>
       </c>
-      <c r="C336" s="39">
+      <c r="C336" s="40">
         <v>503.0</v>
       </c>
-      <c r="D336" s="39">
+      <c r="D336" s="40">
         <v>605.0</v>
       </c>
       <c r="F336" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G336" s="40">
+      <c r="G336" s="41">
         <v>1148.0</v>
       </c>
-      <c r="H336" s="40">
+      <c r="H336" s="41">
         <v>427.0</v>
       </c>
-      <c r="I336" s="40">
+      <c r="I336" s="41">
         <v>1575.0</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="35" t="s">
+      <c r="A337" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B337" s="39">
+      <c r="B337" s="40">
         <v>186.0</v>
       </c>
-      <c r="C337" s="39">
+      <c r="C337" s="40">
         <v>393.0</v>
       </c>
-      <c r="D337" s="39">
+      <c r="D337" s="40">
         <v>579.0</v>
       </c>
       <c r="F337" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G337" s="40">
+      <c r="G337" s="41">
         <v>703.0</v>
       </c>
-      <c r="H337" s="40">
+      <c r="H337" s="41">
         <v>872.0</v>
       </c>
-      <c r="I337" s="40">
+      <c r="I337" s="41">
         <v>1575.0</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="35" t="s">
+      <c r="A338" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B338" s="39">
+      <c r="B338" s="40">
         <v>226.0</v>
       </c>
-      <c r="C338" s="39">
+      <c r="C338" s="40">
         <v>467.0</v>
       </c>
-      <c r="D338" s="39">
+      <c r="D338" s="40">
         <v>693.0</v>
       </c>
       <c r="F338" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G338" s="40">
+      <c r="G338" s="41">
         <v>248.0</v>
       </c>
-      <c r="H338" s="40">
+      <c r="H338" s="41">
         <v>1327.0</v>
       </c>
-      <c r="I338" s="40">
+      <c r="I338" s="41">
         <v>1575.0</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="35" t="s">
+      <c r="A339" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B339" s="39">
+      <c r="B339" s="40">
         <v>266.0</v>
       </c>
-      <c r="C339" s="39">
+      <c r="C339" s="40">
         <v>426.0</v>
       </c>
-      <c r="D339" s="39">
+      <c r="D339" s="40">
         <v>692.0</v>
       </c>
       <c r="F339" s="2" t="s">
@@ -23954,149 +24370,149 @@
       <c r="F340" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G340" s="40">
+      <c r="G340" s="41">
         <v>537.0</v>
       </c>
-      <c r="H340" s="40">
+      <c r="H340" s="41">
         <v>321.0</v>
       </c>
-      <c r="I340" s="40">
+      <c r="I340" s="41">
         <v>858.0</v>
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="35" t="s">
+      <c r="A341" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B341" s="39">
+      <c r="B341" s="40">
         <v>1148.0</v>
       </c>
-      <c r="C341" s="39">
+      <c r="C341" s="40">
         <v>427.0</v>
       </c>
-      <c r="D341" s="39">
+      <c r="D341" s="40">
         <v>1575.0</v>
       </c>
       <c r="F341" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G341" s="40">
+      <c r="G341" s="41">
         <v>564.0</v>
       </c>
-      <c r="H341" s="40">
+      <c r="H341" s="41">
         <v>485.0</v>
       </c>
-      <c r="I341" s="40">
+      <c r="I341" s="41">
         <v>1049.0</v>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="35" t="s">
+      <c r="A342" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B342" s="39">
+      <c r="B342" s="40">
         <v>504.0</v>
       </c>
-      <c r="C342" s="39">
+      <c r="C342" s="40">
         <v>982.0</v>
       </c>
-      <c r="D342" s="39">
+      <c r="D342" s="40">
         <v>1486.0</v>
       </c>
       <c r="F342" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G342" s="40">
+      <c r="G342" s="41">
         <v>308.0</v>
       </c>
-      <c r="H342" s="40">
+      <c r="H342" s="41">
         <v>500.0</v>
       </c>
-      <c r="I342" s="40">
+      <c r="I342" s="41">
         <v>808.0</v>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="35" t="s">
+      <c r="A343" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B343" s="39">
+      <c r="B343" s="40">
         <v>145.0</v>
       </c>
-      <c r="C343" s="39">
+      <c r="C343" s="40">
         <v>1430.0</v>
       </c>
-      <c r="D343" s="39">
+      <c r="D343" s="40">
         <v>1575.0</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="35" t="s">
+      <c r="A344" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B344" s="39">
+      <c r="B344" s="40">
         <v>703.0</v>
       </c>
-      <c r="C344" s="39">
+      <c r="C344" s="40">
         <v>872.0</v>
       </c>
-      <c r="D344" s="39">
+      <c r="D344" s="40">
         <v>1575.0</v>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="35" t="s">
+      <c r="A345" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B345" s="39">
+      <c r="B345" s="40">
         <v>1155.0</v>
       </c>
-      <c r="C345" s="39">
+      <c r="C345" s="40">
         <v>420.0</v>
       </c>
-      <c r="D345" s="39">
+      <c r="D345" s="40">
         <v>1575.0</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="35" t="s">
+      <c r="A346" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B346" s="39">
+      <c r="B346" s="40">
         <v>306.0</v>
       </c>
-      <c r="C346" s="39">
+      <c r="C346" s="40">
         <v>1269.0</v>
       </c>
-      <c r="D346" s="39">
+      <c r="D346" s="40">
         <v>1575.0</v>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="35" t="s">
+      <c r="A347" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B347" s="39">
+      <c r="B347" s="40">
         <v>248.0</v>
       </c>
-      <c r="C347" s="39">
+      <c r="C347" s="40">
         <v>1327.0</v>
       </c>
-      <c r="D347" s="39">
+      <c r="D347" s="40">
         <v>1575.0</v>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="35" t="s">
+      <c r="A348" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B348" s="39">
+      <c r="B348" s="40">
         <v>528.0</v>
       </c>
-      <c r="C348" s="39">
+      <c r="C348" s="40">
         <v>1047.0</v>
       </c>
-      <c r="D348" s="39">
+      <c r="D348" s="40">
         <v>1575.0</v>
       </c>
     </row>
@@ -24106,114 +24522,114 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="35" t="s">
+      <c r="A350" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B350" s="39">
+      <c r="B350" s="40">
         <v>537.0</v>
       </c>
-      <c r="C350" s="39">
+      <c r="C350" s="40">
         <v>321.0</v>
       </c>
-      <c r="D350" s="39">
+      <c r="D350" s="40">
         <v>858.0</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="35" t="s">
+      <c r="A351" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B351" s="39">
+      <c r="B351" s="40">
         <v>133.0</v>
       </c>
-      <c r="C351" s="39">
+      <c r="C351" s="40">
         <v>718.0</v>
       </c>
-      <c r="D351" s="39">
+      <c r="D351" s="40">
         <v>851.0</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="35" t="s">
+      <c r="A352" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B352" s="39">
+      <c r="B352" s="40">
         <v>159.0</v>
       </c>
-      <c r="C352" s="39">
+      <c r="C352" s="40">
         <v>914.0</v>
       </c>
-      <c r="D352" s="39">
+      <c r="D352" s="40">
         <v>1073.0</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="35" t="s">
+      <c r="A353" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B353" s="39">
+      <c r="B353" s="40">
         <v>564.0</v>
       </c>
-      <c r="C353" s="39">
+      <c r="C353" s="40">
         <v>485.0</v>
       </c>
-      <c r="D353" s="39">
+      <c r="D353" s="40">
         <v>1049.0</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="35" t="s">
+      <c r="A354" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B354" s="39">
+      <c r="B354" s="40">
         <v>612.0</v>
       </c>
-      <c r="C354" s="39">
+      <c r="C354" s="40">
         <v>277.0</v>
       </c>
-      <c r="D354" s="39">
+      <c r="D354" s="40">
         <v>889.0</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="35" t="s">
+      <c r="A355" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B355" s="39">
+      <c r="B355" s="40">
         <v>261.0</v>
       </c>
-      <c r="C355" s="39">
+      <c r="C355" s="40">
         <v>330.0</v>
       </c>
-      <c r="D355" s="39">
+      <c r="D355" s="40">
         <v>591.0</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="35" t="s">
+      <c r="A356" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B356" s="39">
+      <c r="B356" s="40">
         <v>308.0</v>
       </c>
-      <c r="C356" s="39">
+      <c r="C356" s="40">
         <v>500.0</v>
       </c>
-      <c r="D356" s="39">
+      <c r="D356" s="40">
         <v>808.0</v>
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="35" t="s">
+      <c r="A357" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B357" s="39">
+      <c r="B357" s="40">
         <v>209.0</v>
       </c>
-      <c r="C357" s="39">
+      <c r="C357" s="40">
         <v>374.0</v>
       </c>
-      <c r="D357" s="39">
+      <c r="D357" s="40">
         <v>583.0</v>
       </c>
     </row>
